--- a/artfynd/A 61865-2020 artfynd.xlsx
+++ b/artfynd/A 61865-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685518</v>
       </c>
       <c r="B2" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128685517</v>
       </c>
       <c r="B3" t="n">
-        <v>58227</v>
+        <v>58254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61865-2020 artfynd.xlsx
+++ b/artfynd/A 61865-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685518</v>
       </c>
       <c r="B2" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128685517</v>
       </c>
       <c r="B3" t="n">
-        <v>58254</v>
+        <v>58258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61865-2020 artfynd.xlsx
+++ b/artfynd/A 61865-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,228 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128974412</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rishorvan, Södra Sandby, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>599432</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6269553</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sandby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Tallroth</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Tallroth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128974415</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58437</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rishorvan, Södra Sandby, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>599432</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6269553</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sandby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Tallroth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Tallroth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61865-2020 artfynd.xlsx
+++ b/artfynd/A 61865-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685518</v>
       </c>
       <c r="B2" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128685517</v>
       </c>
       <c r="B3" t="n">
-        <v>58258</v>
+        <v>58261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128974412</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>128974415</v>
       </c>
       <c r="B5" t="n">
-        <v>58437</v>
+        <v>58440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61865-2020 artfynd.xlsx
+++ b/artfynd/A 61865-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685518</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128685517</v>
       </c>
       <c r="B3" t="n">
-        <v>58261</v>
+        <v>58263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128974412</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>128974415</v>
       </c>
       <c r="B5" t="n">
-        <v>58440</v>
+        <v>58442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61865-2020 artfynd.xlsx
+++ b/artfynd/A 61865-2020 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128974412</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>128974415</v>
       </c>
       <c r="B5" t="n">
-        <v>58442</v>
+        <v>58444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
